--- a/Design/config/SeasonConfig.xlsx
+++ b/Design/config/SeasonConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -65,10 +65,6 @@
     <t>dong</t>
   </si>
   <si>
-    <t>dong</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>chun</t>
   </si>
   <si>
@@ -78,40 +74,156 @@
     <t>qiu</t>
   </si>
   <si>
-    <t>一月 冬</t>
-  </si>
-  <si>
-    <t>二月 冬</t>
-  </si>
-  <si>
-    <t>三月 春</t>
-  </si>
-  <si>
-    <t>四月 春</t>
-  </si>
-  <si>
-    <t>五月 春</t>
-  </si>
-  <si>
-    <t>六月 夏</t>
-  </si>
-  <si>
-    <t>七月 夏</t>
-  </si>
-  <si>
-    <t>八月 夏</t>
-  </si>
-  <si>
-    <t>九月 秋</t>
-  </si>
-  <si>
-    <t>十月 秋</t>
-  </si>
-  <si>
-    <t>十一月 秋</t>
-  </si>
-  <si>
-    <t>十二月 冬</t>
+    <t>一月一日</t>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>一月十日</t>
+  </si>
+  <si>
+    <t>一月二十日</t>
+  </si>
+  <si>
+    <t>二月一日</t>
+  </si>
+  <si>
+    <t>二月十日</t>
+  </si>
+  <si>
+    <t>二月二十日</t>
+  </si>
+  <si>
+    <t>三月一日</t>
+  </si>
+  <si>
+    <t>春</t>
+  </si>
+  <si>
+    <t>三月十日</t>
+  </si>
+  <si>
+    <t>三月二十日</t>
+  </si>
+  <si>
+    <t>四月一日</t>
+  </si>
+  <si>
+    <t>四月十日</t>
+  </si>
+  <si>
+    <t>四月二十日</t>
+  </si>
+  <si>
+    <t>五月一日</t>
+  </si>
+  <si>
+    <t>五月十日</t>
+  </si>
+  <si>
+    <t>五月二十日</t>
+  </si>
+  <si>
+    <t>六月一日</t>
+  </si>
+  <si>
+    <t>夏</t>
+  </si>
+  <si>
+    <t>六月十日</t>
+  </si>
+  <si>
+    <t>六月二十日</t>
+  </si>
+  <si>
+    <t>七月一日</t>
+  </si>
+  <si>
+    <t>七月十日</t>
+  </si>
+  <si>
+    <t>七月二十日</t>
+  </si>
+  <si>
+    <t>八月一日</t>
+  </si>
+  <si>
+    <t>八月十日</t>
+  </si>
+  <si>
+    <t>八月二十日</t>
+  </si>
+  <si>
+    <t>九月一日</t>
+  </si>
+  <si>
+    <t>秋</t>
+  </si>
+  <si>
+    <t>九月十日</t>
+  </si>
+  <si>
+    <t>九月二十日</t>
+  </si>
+  <si>
+    <t>十月一日</t>
+  </si>
+  <si>
+    <t>十月十日</t>
+  </si>
+  <si>
+    <t>十月二十日</t>
+  </si>
+  <si>
+    <t>十一月一日</t>
+  </si>
+  <si>
+    <t>十一月十日</t>
+  </si>
+  <si>
+    <t>十一月二十日</t>
+  </si>
+  <si>
+    <t>十二月一日</t>
+  </si>
+  <si>
+    <t>十二月十日</t>
+  </si>
+  <si>
+    <t>十二月二十日</t>
+  </si>
+  <si>
+    <t>Season</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>季节</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发钱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发米</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddGold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AddFood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -506,15 +618,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="12.125" customWidth="1"/>
+    <col min="2" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="5" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,10 +634,19 @@
         <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -533,10 +654,19 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -546,8 +676,17 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="D3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -557,19 +696,35 @@
       <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="D4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -577,10 +732,15 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -588,12 +748,15 @@
         <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -601,12 +764,17 @@
         <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -614,12 +782,17 @@
         <v>19</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -627,12 +800,17 @@
         <v>20</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -640,83 +818,523 @@
         <v>21</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="D11" s="4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4">
+        <v>6</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="4">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="4">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="4">
+        <v>3</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4">
+        <v>20</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
         <v>26</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="B30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
+        <v>28</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="4">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <v>30</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4">
+        <v>6</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>32</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="4">
+        <v>3</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-    </row>
-    <row r="17" spans="21:22" x14ac:dyDescent="0.2">
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-    </row>
-    <row r="18" spans="21:22" x14ac:dyDescent="0.2">
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:C4">

--- a/Design/config/SeasonConfig.xlsx
+++ b/Design/config/SeasonConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="66">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -223,6 +223,22 @@
   </si>
   <si>
     <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>视频</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Video</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>goldin.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>harve2.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -645,6 +661,9 @@
       <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -665,6 +684,9 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -685,6 +707,9 @@
       <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -705,6 +730,9 @@
       <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
@@ -722,6 +750,9 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
@@ -739,6 +770,7 @@
       <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
@@ -755,6 +787,7 @@
       <c r="F7" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
@@ -772,6 +805,9 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
@@ -789,6 +825,7 @@
       <c r="F9" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="G9" s="4"/>
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
     </row>
@@ -807,6 +844,7 @@
       <c r="F10" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="G10" s="4"/>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
     </row>
@@ -826,6 +864,9 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
         <v>11</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
@@ -845,6 +886,7 @@
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="G12" s="4"/>
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
     </row>
@@ -863,6 +905,7 @@
       <c r="F13" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="G13" s="4"/>
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
     </row>
@@ -882,6 +925,9 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4" t="s">
         <v>11</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
@@ -901,6 +947,7 @@
       <c r="F15" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="G15" s="4"/>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
@@ -921,6 +968,9 @@
       <c r="F16" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="G16" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
     </row>
@@ -940,6 +990,9 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
         <v>11</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
@@ -959,6 +1012,7 @@
       <c r="F18" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="G18" s="4"/>
       <c r="W18" s="5"/>
       <c r="X18" s="5"/>
     </row>
@@ -977,6 +1031,7 @@
       <c r="F19" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="G19" s="4"/>
       <c r="W19" s="5"/>
       <c r="X19" s="5"/>
     </row>
@@ -996,6 +1051,9 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
@@ -1015,6 +1073,7 @@
       <c r="F21" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
@@ -1031,6 +1090,7 @@
       <c r="F22" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
@@ -1048,6 +1108,9 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
@@ -1065,6 +1128,7 @@
       <c r="F24" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
@@ -1083,6 +1147,9 @@
       <c r="F25" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="G25" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
@@ -1100,6 +1167,9 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
@@ -1117,6 +1187,7 @@
       <c r="F27" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
@@ -1133,6 +1204,7 @@
       <c r="F28" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
@@ -1150,6 +1222,9 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
         <v>13</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
@@ -1167,6 +1242,7 @@
       <c r="F30" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
@@ -1183,6 +1259,7 @@
       <c r="F31" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
@@ -1201,8 +1278,11 @@
       <c r="F32" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G32" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>29</v>
       </c>
@@ -1217,8 +1297,9 @@
       <c r="F33" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>30</v>
       </c>
@@ -1235,8 +1316,11 @@
       <c r="F34" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G34" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>31</v>
       </c>
@@ -1253,8 +1337,11 @@
       <c r="F35" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G35" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>32</v>
       </c>
@@ -1269,8 +1356,9 @@
       <c r="F36" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>33</v>
       </c>
@@ -1285,8 +1373,9 @@
       <c r="F37" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>34</v>
       </c>
@@ -1303,8 +1392,11 @@
       <c r="F38" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G38" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>35</v>
       </c>
@@ -1319,8 +1411,9 @@
       <c r="F39" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>36</v>
       </c>
@@ -1335,6 +1428,7 @@
       <c r="F40" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="G40" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:C4">

--- a/Design/config/SeasonConfig.xlsx
+++ b/Design/config/SeasonConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="60">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -199,30 +199,6 @@
   </si>
   <si>
     <t>季节</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发钱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>发米</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddGold</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddFood</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -634,15 +610,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.875" customWidth="1"/>
-    <col min="3" max="5" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -653,19 +629,13 @@
         <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -676,19 +646,13 @@
         <v>54</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -699,19 +663,13 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -722,19 +680,13 @@
         <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -744,18 +696,14 @@
       <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E5" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -765,14 +713,12 @@
       <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -782,14 +728,12 @@
       <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>4</v>
       </c>
@@ -799,18 +743,14 @@
       <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E8" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
@@ -820,16 +760,14 @@
       <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
@@ -839,16 +777,14 @@
       <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -858,20 +794,16 @@
       <c r="C11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4">
-        <v>3</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>8</v>
       </c>
@@ -881,16 +813,14 @@
       <c r="C12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -900,16 +830,14 @@
       <c r="C13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>10</v>
       </c>
@@ -919,20 +847,16 @@
       <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="4">
-        <v>3</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -942,16 +866,14 @@
       <c r="C15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E15" s="4"/>
-      <c r="F15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>12</v>
       </c>
@@ -961,20 +883,16 @@
       <c r="C16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4">
-        <v>6</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>13</v>
       </c>
@@ -984,20 +902,16 @@
       <c r="C17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="4">
-        <v>3</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>14</v>
       </c>
@@ -1007,16 +921,14 @@
       <c r="C18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>15</v>
       </c>
@@ -1026,16 +938,14 @@
       <c r="C19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="E19" s="4"/>
-      <c r="F19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>16</v>
       </c>
@@ -1045,20 +955,16 @@
       <c r="C20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="4">
-        <v>3</v>
-      </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>17</v>
       </c>
@@ -1068,14 +974,12 @@
       <c r="C21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E21" s="4"/>
-      <c r="F21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>18</v>
       </c>
@@ -1085,14 +989,12 @@
       <c r="C22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E22" s="4"/>
-      <c r="F22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -1102,18 +1004,14 @@
       <c r="C23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="4">
-        <v>3</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E23" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>20</v>
       </c>
@@ -1123,14 +1021,12 @@
       <c r="C24" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>21</v>
       </c>
@@ -1140,18 +1036,14 @@
       <c r="C25" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4">
-        <v>20</v>
-      </c>
-      <c r="F25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E25" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>22</v>
       </c>
@@ -1161,18 +1053,14 @@
       <c r="C26" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="4">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E26" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>23</v>
       </c>
@@ -1182,14 +1070,12 @@
       <c r="C27" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E27" s="4"/>
-      <c r="F27" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>24</v>
       </c>
@@ -1199,14 +1085,12 @@
       <c r="C28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>25</v>
       </c>
@@ -1216,18 +1100,14 @@
       <c r="C29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="4">
-        <v>3</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E29" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>26</v>
       </c>
@@ -1237,14 +1117,12 @@
       <c r="C30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E30" s="4"/>
-      <c r="F30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>27</v>
       </c>
@@ -1254,14 +1132,12 @@
       <c r="C31" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E31" s="4"/>
-      <c r="F31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>28</v>
       </c>
@@ -1271,18 +1147,14 @@
       <c r="C32" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="4">
-        <v>3</v>
-      </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E32" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>29</v>
       </c>
@@ -1292,14 +1164,12 @@
       <c r="C33" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E33" s="4"/>
-      <c r="F33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>30</v>
       </c>
@@ -1309,18 +1179,14 @@
       <c r="C34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4">
-        <v>6</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E34" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>31</v>
       </c>
@@ -1330,18 +1196,14 @@
       <c r="C35" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="4">
-        <v>3</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E35" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>32</v>
       </c>
@@ -1351,14 +1213,12 @@
       <c r="C36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E36" s="4"/>
-      <c r="F36" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>33</v>
       </c>
@@ -1368,14 +1228,12 @@
       <c r="C37" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="4"/>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E37" s="4"/>
-      <c r="F37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="4"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>34</v>
       </c>
@@ -1385,18 +1243,14 @@
       <c r="C38" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="4">
-        <v>3</v>
-      </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E38" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>35</v>
       </c>
@@ -1406,14 +1260,12 @@
       <c r="C39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="4"/>
+      <c r="D39" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E39" s="4"/>
-      <c r="F39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="4"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>36</v>
       </c>
@@ -1423,12 +1275,10 @@
       <c r="C40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="4"/>
+      <c r="D40" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E40" s="4"/>
-      <c r="F40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:C4">
